--- a/tools/dim/out/kimya_dim_yoxlama.xlsx
+++ b/tools/dim/out/kimya_dim_yoxlama.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y121"/>
+  <dimension ref="A1:Z121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -585,6 +585,11 @@
           <t>sinif</t>
         </is>
       </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>izah şəkli</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -652,7 +657,9 @@
           <t>D</t>
         </is>
       </c>
-      <c r="N2" s="2" t="inlineStr"/>
+      <c r="N2" s="2" t="n">
+        <v>3</v>
+      </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
           <t>Alkenlər $\mathrm{C_{n}H_{2n}}$ ümumi formuluna malikdirlər. Ümumi formuldan göründüyü kimi alken molekulunda hidrogen atomlarının sayı karbon atomlarının sayından 2 dəfə çoxdur. Əgər hidrogen atomlarının sayı 2n – 2 olarsa, karbon atomlarının sayı n – 1 olacaq.</t>
@@ -690,7 +697,7 @@
       </c>
       <c r="V2" s="2" t="inlineStr">
         <is>
-          <t>xeyr</t>
+          <t>bəli</t>
         </is>
       </c>
       <c r="W2" s="2" t="inlineStr">
@@ -706,6 +713,11 @@
       <c r="Y2" s="2" t="inlineStr">
         <is>
           <t>10</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>KIM-0001_izah.png</t>
         </is>
       </c>
     </row>
@@ -775,7 +787,9 @@
           <t>D</t>
         </is>
       </c>
-      <c r="N3" s="2" t="inlineStr"/>
+      <c r="N3" s="2" t="n">
+        <v>3</v>
+      </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
           <t>Etiltsiklobutan molekulunda ümumilikdə 6 karbon atomu var. Onlardan biri birli, dördü ikili, biri isə üçlüdür. Etiltsiklobutan molekulunda 18 siqma rabitə, 24 hibrid orbital var. Metiltsiklobutan molekulunda cəmi 5 karbon atomu var. Onlardan biri birli, üçü ikili, biri isə üçlüdür. Metiltsiklobutan molekulunda 15 siqma rabitə, 20 hibrid orbital var.</t>
@@ -813,7 +827,7 @@
       </c>
       <c r="V3" s="2" t="inlineStr">
         <is>
-          <t>xeyr</t>
+          <t>bəli</t>
         </is>
       </c>
       <c r="W3" s="2" t="inlineStr">
@@ -829,6 +843,11 @@
       <c r="Y3" s="2" t="inlineStr">
         <is>
           <t>10</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>KIM-0002_izah.png</t>
         </is>
       </c>
     </row>
@@ -898,7 +917,9 @@
           <t>E</t>
         </is>
       </c>
-      <c r="N4" s="2" t="inlineStr"/>
+      <c r="N4" s="2" t="n">
+        <v>3</v>
+      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
           <t>Aldehidlərin $\mathrm{Ag_{2}O}$-nun ammonyaklı suda məhlulu ilə reaksiyasından molekulunda eyni sayda karbonu olan doymuş birəsaslı karbon turşuları, hidrogenləşməsindən isə molekulunda eyni sayda karbonu olan doymuş biratomlu spirtlər alınır</t>
@@ -936,7 +957,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>xeyr</t>
+          <t>bəli</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -952,6 +973,11 @@
       <c r="Y4" s="2" t="inlineStr">
         <is>
           <t>11</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>KIM-0003_izah.png</t>
         </is>
       </c>
     </row>
@@ -1021,7 +1047,9 @@
           <t>C</t>
         </is>
       </c>
-      <c r="N5" s="2" t="inlineStr"/>
+      <c r="N5" s="2" t="n">
+        <v>3</v>
+      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
           <t>X $\mathrm{_{(q)} + Y_{(q)}}$ ⇌ Z (q) Reaksiya tənliyindən görünür ki, reaksiyaya daxil olan və alınan maddələrin mol nisbəti eynidir. Belə ki, tarazlıq anına qədər a mol X ilə reaksiyaya a mol Y sərf olunur və a mol Z alınır. Tarazlıq anında qabda 8 – a mol X , 6 – a mol Y və a mol Z qazı olur. Bu qazların cəmi 10 mol olduğunu nəzərə alsaq, 8 – a + 6 – a + a = 10 ifadəsindən a = 4 olur. $\mathrm{K_{T} = C_{Z}/}$ $\mathrm{(C_{X}\cdot}$ $\mathrm{C_{Y})=}$ 4 / (4 · 2) = 0,5</t>
@@ -1059,7 +1087,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>xeyr</t>
+          <t>bəli</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -1075,6 +1103,11 @@
       <c r="Y5" s="2" t="inlineStr">
         <is>
           <t>8</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>KIM-0004_izah.png</t>
         </is>
       </c>
     </row>
@@ -1196,6 +1229,11 @@
           <t>11</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>KIM-0005_izah.png</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -1317,6 +1355,11 @@
       <c r="Y7" s="2" t="inlineStr">
         <is>
           <t>9</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>KIM-0006_izah.png</t>
         </is>
       </c>
     </row>
@@ -1432,6 +1475,11 @@
           <t>8</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>KIM-0007_izah.png</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
@@ -1545,6 +1593,11 @@
           <t>7</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>KIM-0008_izah.png</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -1666,6 +1719,11 @@
       <c r="Y10" s="2" t="inlineStr">
         <is>
           <t>9</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>KIM-0009_izah.png</t>
         </is>
       </c>
     </row>
@@ -1787,6 +1845,11 @@
           <t>9</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>KIM-0010_izah.png</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
@@ -1900,6 +1963,11 @@
           <t>11</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>KIM-0011_izah.png</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -1967,7 +2035,9 @@
           <t>C</t>
         </is>
       </c>
-      <c r="N13" s="2" t="inlineStr"/>
+      <c r="N13" s="2" t="n">
+        <v>3</v>
+      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
           <t>S + $\mathrm{I_{2}}$ → reaksiya getmir S + $\mathrm{F_{2} \rightarrow SF_{6}}$ B) $\mathrm{Na_{2}O + H_{2}O \rightarrow NaOH}$ $\mathrm{Si + H_{2}}$ → reaksiya getmir C) $\mathrm{Na_{2}O + H_{2}O \rightarrow NaOH}$ S + $\mathrm{F_{2} \rightarrow SF_{6}}$ D) $\mathrm{CO + CH_{3}OH \rightarrow CH_{3}COOH}$ S + $\mathrm{I_{2}}$ → reaksiya getmir E) P + $\mathrm{H_{2}}$ → reaksiya getmir $\mathrm{Si + H_{2}}$ → reaksiya getmir</t>
@@ -2005,7 +2075,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>xeyr</t>
+          <t>bəli</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -2021,6 +2091,11 @@
       <c r="Y13" s="2" t="inlineStr">
         <is>
           <t>9</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>KIM-0012_izah.png</t>
         </is>
       </c>
     </row>
@@ -2090,7 +2165,9 @@
           <t>B</t>
         </is>
       </c>
-      <c r="N14" s="2" t="inlineStr"/>
+      <c r="N14" s="2" t="n">
+        <v>3</v>
+      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
           <t>$\mathrm{C_{4}H_{10} \rightarrow C_{2}H_{6} + C_{2}H_{4}}$ $\mathrm{C_{2}H_{4} + Cl_{2} \rightarrow C_{2}H_{4}Cl_{2}}$ $\mathrm{C_{2}H_{4}Cl_{2} + 2KOH_{(su)} \rightarrow 2KCl + C_{2}H_{4}(OH)_{2}}$</t>
@@ -2128,7 +2205,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>xeyr</t>
+          <t>bəli</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2144,6 +2221,11 @@
       <c r="Y14" s="2" t="inlineStr">
         <is>
           <t>11</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>KIM-0013_izah.png</t>
         </is>
       </c>
     </row>
@@ -2259,6 +2341,11 @@
           <t>8</t>
         </is>
       </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>KIM-0014_izah.png</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
@@ -2372,6 +2459,11 @@
           <t>8</t>
         </is>
       </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>KIM-0015_izah.png</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -2439,7 +2531,9 @@
           <t>A</t>
         </is>
       </c>
-      <c r="N17" s="2" t="inlineStr"/>
+      <c r="N17" s="2" t="n">
+        <v>3</v>
+      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
           <t>Xlorun həyəcanlanmış hallarına uyğun elektron formullarında tək elektron sayını hesablayaq ... $\mathrm{3s^{1}3p^{3}3d^{3}}$ – 7 tək elektron ,7 valentlidir, oksidləşmə dərəcəsi +7 olur. ... $\mathrm{3s^{2}3p^{4}3d^{1}}$ – 3 tək elektron, 3 valentlidir, oksidləşmə dərəcəsi +3 olur. ... $\mathrm{3s^{2}3p^{3}3d^{2}}$ – 5 tək elektron, 5 valentlidir, oksidləşmə dərəcəsi +5 olur.</t>
@@ -2477,7 +2571,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>xeyr</t>
+          <t>bəli</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2493,6 +2587,11 @@
       <c r="Y17" s="2" t="inlineStr">
         <is>
           <t>9</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>KIM-0016_izah.png</t>
         </is>
       </c>
     </row>
@@ -2562,7 +2661,9 @@
           <t>B</t>
         </is>
       </c>
-      <c r="N18" s="2" t="inlineStr"/>
+      <c r="N18" s="2" t="n">
+        <v>3</v>
+      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
           <t>proton,neytron və elektron saylarından aydın olur ki, X və T neytral atomdur. X və Z izotop,Y kation, Z isə aniondur. T-nin kütlə ədədi 39-dur. X və Z-in elektron sayı eynidir.</t>
@@ -2600,7 +2701,7 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>xeyr</t>
+          <t>bəli</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
@@ -2616,6 +2717,11 @@
       <c r="Y18" s="2" t="inlineStr">
         <is>
           <t>8</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>KIM-0017_izah.png</t>
         </is>
       </c>
     </row>
@@ -2731,6 +2837,11 @@
           <t>9</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>KIM-0018_izah.png</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -2798,7 +2909,9 @@
           <t>B</t>
         </is>
       </c>
-      <c r="N20" s="2" t="inlineStr"/>
+      <c r="N20" s="2" t="n">
+        <v>3</v>
+      </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
           <t>$\mathrm{MgHPO_{4}}$ – maqnezium-hidroortofosfat, turş duzdur</t>
@@ -2836,7 +2949,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>xeyr</t>
+          <t>bəli</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2852,6 +2965,11 @@
       <c r="Y20" s="2" t="inlineStr">
         <is>
           <t>8</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>KIM-0019_izah.png</t>
         </is>
       </c>
     </row>
@@ -2921,7 +3039,9 @@
           <t>A</t>
         </is>
       </c>
-      <c r="N21" s="2" t="inlineStr"/>
+      <c r="N21" s="2" t="n">
+        <v>3</v>
+      </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
           <t>$\mathrm{Cu(NO_{3})_{2} \rightarrow CuO}$ (əsasi oksid) + $\mathrm{NO_{2}}$ (turşu oksidi) + $\mathrm{O_{2}}$ $\mathrm{NaNO_{3} \rightarrow NaNO_{2} + O_{2}}$ $\mathrm{AgNO_{3} \rightarrow Ag + NO_{2} + O_{2}}$ $\mathrm{NH_{4}NO_{3} \rightarrow N_{2}O + H_{2}O}$ $\mathrm{KNO_{3} \rightarrow KNO_{2} + O_{2}}$</t>
@@ -2955,7 +3075,7 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>xeyr</t>
+          <t>bəli</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
@@ -2971,6 +3091,11 @@
       <c r="Y21" s="2" t="inlineStr">
         <is>
           <t>9</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>KIM-0020_izah.png</t>
         </is>
       </c>
     </row>
@@ -3040,7 +3165,9 @@
           <t>B</t>
         </is>
       </c>
-      <c r="N22" s="2" t="inlineStr"/>
+      <c r="N22" s="2" t="n">
+        <v>3</v>
+      </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
           <t>Hər 3 qabda $\mathrm{CuSO_{4}}$ – ün kütləsi: $\mathrm{m(CuSO_{4})}$ = 200 ⋅ 0,16 = 32 q 32 q x q $\mathrm{Fe + CuSO_{4} \rightarrow FeSO_{4} + Cu}$ x = 12,8 q 160 q 64 q $\mathrm{Ag + CuSO_{4}}$ → reaksiya getmir 32 q y q $\mathrm{Zn + CuSO_{4} \rightarrow ZnSO_{4} + Cu}$ y = 12,8 q 160 q 64 q Reaksiyalardan alınan $\mathrm{Cu}$-un kütləsi = 12,8 + 12,8 = 25,6 q</t>
@@ -3078,7 +3205,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>xeyr</t>
+          <t>bəli</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -3094,6 +3221,11 @@
       <c r="Y22" s="2" t="inlineStr">
         <is>
           <t>9</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>KIM-0021_izah.png</t>
         </is>
       </c>
     </row>
@@ -3217,6 +3349,11 @@
       <c r="Y23" s="2" t="inlineStr">
         <is>
           <t>9</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>KIM-0022_izah.png</t>
         </is>
       </c>
     </row>
@@ -3312,6 +3449,11 @@
           <t>11</t>
         </is>
       </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>KIM-0023_izah.png</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
@@ -3405,6 +3547,11 @@
           <t>10</t>
         </is>
       </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>KIM-0024_izah.png</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -3504,6 +3651,11 @@
           <t>11</t>
         </is>
       </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>KIM-0025_izah.png</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -3551,7 +3703,9 @@
           <t>20</t>
         </is>
       </c>
-      <c r="N27" s="2" t="inlineStr"/>
+      <c r="N27" s="2" t="n">
+        <v>3</v>
+      </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
           <t>x q ------------------- 23,3 q $\mathrm{H_{2}SO_{4} + BaCl_{2} \rightarrow BaSO_{4}}$ ↓ + $\mathrm{2HCl}$ x = 9,8 q $\mathrm{H_{2}SO_{4}}$ 98 q ------------------- 233 q Məhlulda sulfat turşusunun kütlə payı = (9,8 : 49) ⋅ 100 = 20%</t>
@@ -3589,7 +3743,7 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>xeyr</t>
+          <t>bəli</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
@@ -3605,6 +3759,11 @@
       <c r="Y27" s="2" t="inlineStr">
         <is>
           <t>7</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>KIM-0026_izah.png</t>
         </is>
       </c>
     </row>
@@ -3710,6 +3869,11 @@
           <t>10</t>
         </is>
       </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>KIM-0027_izah.png</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -3809,6 +3973,11 @@
           <t>8</t>
         </is>
       </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>KIM-0028_izah.png</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -3906,6 +4075,11 @@
       <c r="Y30" s="2" t="inlineStr">
         <is>
           <t>8</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>KIM-0029_izah.png</t>
         </is>
       </c>
     </row>
@@ -4003,6 +4177,11 @@
           <t>8</t>
         </is>
       </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>KIM-0030_izah.png</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -4070,7 +4249,9 @@
           <t>D</t>
         </is>
       </c>
-      <c r="N32" s="2" t="inlineStr"/>
+      <c r="N32" s="2" t="n">
+        <v>3</v>
+      </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
           <t>2n + 1 = 5 2n = 4 n = 2 $\mathrm{C_{2}H_{5}COOH}$ turşusu ilə siniflərarası izomer olan maddənin hidroliz tənliyi: $\mathrm{HCOOC_{2}H_{5}+}$ $\mathrm{H_{2}O \Leftrightarrow HCOOH + C_{2}H_{5}OH}$ $\mathrm{HCOOH}$ “gümüş-güzgü” reaksiyasına daxil olduğu üçün X maddəsi $\mathrm{C_{2}H_{5}OH}$-dır və molekulunda 9 atomu var.</t>
@@ -4108,7 +4289,7 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>xeyr</t>
+          <t>bəli</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
@@ -4124,6 +4305,11 @@
       <c r="Y32" s="2" t="inlineStr">
         <is>
           <t>11</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>KIM-0031_izah.png</t>
         </is>
       </c>
     </row>
@@ -4239,6 +4425,11 @@
           <t>7</t>
         </is>
       </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>KIM-0032_izah.png</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -4306,7 +4497,9 @@
           <t>A</t>
         </is>
       </c>
-      <c r="N34" s="2" t="inlineStr"/>
+      <c r="N34" s="2" t="n">
+        <v>3</v>
+      </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
           <t>Hər üç molekulda mərkəzi atom $\mathrm{sp^{3}}$ hibrid halında olub 4 hibrid orbitalına malikdir. $\mathrm{CH_{4}}$ molekulunda 4 hibrid orbitalının hamısı, $\mathrm{NH_{3}}$ molekulunda 3-ü, $\mathrm{H_{2}O}$ molekulunda isə 2-si rabitələrin yaranmasında iştirak edir.</t>
@@ -4344,7 +4537,7 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>xeyr</t>
+          <t>bəli</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
@@ -4360,6 +4553,11 @@
       <c r="Y34" s="2" t="inlineStr">
         <is>
           <t>8</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>KIM-0033_izah.png</t>
         </is>
       </c>
     </row>
@@ -4429,7 +4627,9 @@
           <t>A</t>
         </is>
       </c>
-      <c r="N35" s="2" t="inlineStr"/>
+      <c r="N35" s="2" t="n">
+        <v>3</v>
+      </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
           <t>Şəkildən göründüyü kimi Y elektrodu katoddur (mənfi yüklü olduğu üçün) və elektroliz prosesi zamanı bu elektrodda $\mathrm{Cu}$ alınır. (400⋅20) : 100 = 80 q $\mathrm{CuSO_{4}}$ 80 q x q $\mathrm{2CuSO_{4} + 2H_{2}O}$ → 2Cu + $\mathrm{2H_{2}SO_{4} + O_{2}}$ 2·160 q 2·64 q 80 q $\mathrm{CuSO_{4}-------}$ x q $\mathrm{Cu}$ 2·160 q $\mathrm{CuSO_{4}----}$ 2·64 q $\mathrm{Cu}$ x = 32 q $\mathrm{Cu}$</t>
@@ -4467,7 +4667,7 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>xeyr</t>
+          <t>bəli</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
@@ -4483,6 +4683,11 @@
       <c r="Y35" s="2" t="inlineStr">
         <is>
           <t>8</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>KIM-0034_izah.png</t>
         </is>
       </c>
     </row>
@@ -4552,7 +4757,9 @@
           <t>E</t>
         </is>
       </c>
-      <c r="N36" s="2" t="inlineStr"/>
+      <c r="N36" s="2" t="n">
+        <v>3</v>
+      </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
           <t>$\mathrm{H_{2}SO_{4}}$ (qatı) + $\mathrm{Na \rightarrow H_{2}S + SO \rightarrow ^{2},t}$ S $\mathrm{+O^{2},}$ → t, $\mathrm{SO_{2} - (Na_{2}SO_{4}+H_{2}O) - H_{2}O}$ Sxemə əsasən X – $\mathrm{H_{2}S,}$ Y- $\mathrm{H_{2}O,}$ Z- $\mathrm{SO_{2}}$</t>
@@ -4590,7 +4797,7 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>xeyr</t>
+          <t>bəli</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
@@ -4606,6 +4813,11 @@
       <c r="Y36" s="2" t="inlineStr">
         <is>
           <t>9</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>KIM-0035_izah.png</t>
         </is>
       </c>
     </row>
@@ -4721,6 +4933,11 @@
           <t>11</t>
         </is>
       </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>KIM-0036_izah.png</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
@@ -4834,6 +5051,11 @@
           <t>8</t>
         </is>
       </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>KIM-0037_izah.png</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -4901,7 +5123,9 @@
           <t>D</t>
         </is>
       </c>
-      <c r="N39" s="2" t="inlineStr"/>
+      <c r="N39" s="2" t="n">
+        <v>3</v>
+      </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
           <t>$\mathrm{CH_{3}CHO + H_{2} \rightarrow CH_{3}CH_{2}OH}$ $\mathrm{CH_{3}CH_{2}OH + CuO \rightarrow CH_{3}CHO + Cu + H_{2}O}$</t>
@@ -4939,7 +5163,7 @@
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>xeyr</t>
+          <t>bəli</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
@@ -4955,6 +5179,11 @@
       <c r="Y39" s="2" t="inlineStr">
         <is>
           <t>11</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>KIM-0038_izah.png</t>
         </is>
       </c>
     </row>
@@ -5070,6 +5299,11 @@
           <t>10</t>
         </is>
       </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>KIM-0039_izah.png</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
@@ -5183,6 +5417,11 @@
           <t>11</t>
         </is>
       </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>KIM-0040_izah.png</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -5250,7 +5489,9 @@
           <t>C</t>
         </is>
       </c>
-      <c r="N42" s="2" t="inlineStr"/>
+      <c r="N42" s="2" t="n">
+        <v>3</v>
+      </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
           <t>Reaksiya eyni temperaturda və eyni həcmli qablarda baş verir. Eyni temperaturda eyni maddələr arasında baş verdiyi üçün sürət sabiti (k) dəyişmir. Kütlələrin təsiri qanununu tətbiq edərək sürətləri müqayisə edək. Qabların həcmləri bərabər olduğundan müqayisə zamanı qatılıq əvəzinə mol miqdarından istifadə edə bilərik. 14 q $\mathrm{N_{2}}$ = 0,5 mol 14 q $\mathrm{H_{2}}$ = 7 mol $\mathrm{v_{1} = k\cdot [N_{2}]\cdot [H_{2}]^{3}=}$ $\mathrm{k\cdot 0,5\cdot 7^{3}}$ $\mathrm{v_{2} = k\cdot [N_{2}]\cdot [H_{2}]^{3}=}$ $\mathrm{k\cdot 0,5\cdot 14^{3} = k\cdot 4\cdot 7^{3}}$ $\mathrm{v_{3} = k\cdot [N_{2}]\cdot [H_{2}]^{3}=}$ $\mathrm{k\cdot 14\cdot 7^{3}}$ İfadələrin müqayisəsindən aydın olur ki, $\mathrm{v_{3}&gt;v_{2}&gt;v_{1}}$</t>
@@ -5288,7 +5529,7 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>xeyr</t>
+          <t>bəli</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
@@ -5304,6 +5545,11 @@
       <c r="Y42" s="2" t="inlineStr">
         <is>
           <t>8</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>KIM-0041_izah.png</t>
         </is>
       </c>
     </row>
@@ -5419,6 +5665,11 @@
           <t>9</t>
         </is>
       </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>KIM-0042_izah.png</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -5538,6 +5789,11 @@
           <t>9</t>
         </is>
       </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>KIM-0043_izah.png</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -5661,6 +5917,11 @@
           <t>11</t>
         </is>
       </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>KIM-0044_izah.png</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -5784,6 +6045,11 @@
           <t>10</t>
         </is>
       </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>KIM-0045_izah.png</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -5851,7 +6117,9 @@
           <t>B</t>
         </is>
       </c>
-      <c r="N47" s="2" t="inlineStr"/>
+      <c r="N47" s="2" t="n">
+        <v>3</v>
+      </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
           <t>$\mathrm{Fe + HNO_{3} \rightarrow Fe(NO_{3})_{3}+}$ $\mathrm{NO + H_{2}O}$ $\mathrm{Cu + HNO_{3} \rightarrow Cu(NO_{3})_{2}+}$ $\mathrm{NO_{2} + H_{2}O}$ (X maddəsinə uyğun) C + $\mathrm{HNO_{3} \rightarrow CO_{2}+}$ $\mathrm{NO_{2} + H_{2}O}$ (Y maddəsinə uyğun) P + $\mathrm{HNO_{3} \rightarrow H_{3}PO_{4} + NO_{2} + H_{2}O}$ S + $\mathrm{HNO_{3} \rightarrow H_{2}SO_{4}+}$ $\mathrm{NO_{2} + H_{2}O}$ (Z maddəsinə uyğun)</t>
@@ -5889,7 +6157,7 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>xeyr</t>
+          <t>bəli</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
@@ -5905,6 +6173,11 @@
       <c r="Y47" s="2" t="inlineStr">
         <is>
           <t>9</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>KIM-0046_izah.png</t>
         </is>
       </c>
     </row>
@@ -6026,6 +6299,11 @@
           <t>11</t>
         </is>
       </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>KIM-0047_izah.png</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -6093,7 +6371,9 @@
           <t>A</t>
         </is>
       </c>
-      <c r="N49" s="2" t="inlineStr"/>
+      <c r="N49" s="2" t="n">
+        <v>3</v>
+      </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
           <t>Dördüncü dövrün əlavə yarımqrup elementlərinin hər birində 12 p elektronu olduğundan: a + 7 = 12 a = 5 X atomunda elektronların ümumi sayı: a+2 + a+7 + a = 24 24 protonu olan element (X). ... $\mathrm{3d^{5}4s^{1}}$ qısa elektron formuluna malikdir, 6 tək elektronu var və metaldır, VI B qrupunda yerləşir.</t>
@@ -6131,7 +6411,7 @@
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>xeyr</t>
+          <t>bəli</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
@@ -6147,6 +6427,11 @@
       <c r="Y49" s="2" t="inlineStr">
         <is>
           <t>7</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>KIM-0048_izah.png</t>
         </is>
       </c>
     </row>
@@ -6216,7 +6501,9 @@
           <t>A</t>
         </is>
       </c>
-      <c r="N50" s="2" t="inlineStr"/>
+      <c r="N50" s="2" t="n">
+        <v>3</v>
+      </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
           <t>$\mathrm{2KMnO_{4} \rightarrow K_{2}MnO_{4} + MnO_{2} + O_{2}}$ $\mathrm{KClO_{3}+}$ $\mathrm{6HCl \rightarrow 5KCl + 3H_{2}O + 3Cl_{2}}$ $\mathrm{2H_{2}O \rightarrow 2H_{2} + O_{2}}$ Deməli X maddəsi $\mathrm{H_{2}O,}$ Y maddəsi $\mathrm{O_{2}}$-dir. 1. $\mathrm{H_{2}O + Cu}$ → reaksiya getmir 2. $\mathrm{O_{2}+}$ $\mathrm{2CO \rightarrow 2CO_{2}}$ 3. $\mathrm{H_{2}O}$ + S → reaksiya getmir 4. $\mathrm{5O_{2}+}$ $\mathrm{4NH_{3} \rightarrow 4NO + 6H_{2}O}$ 5. $\mathrm{2H_{2}O+}$ $\mathrm{2F_{2} \rightarrow 4HF + O_{2}}$</t>
@@ -6254,7 +6541,7 @@
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>xeyr</t>
+          <t>bəli</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
@@ -6270,6 +6557,11 @@
       <c r="Y50" s="2" t="inlineStr">
         <is>
           <t>9</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>KIM-0049_izah.png</t>
         </is>
       </c>
     </row>
@@ -6395,6 +6687,11 @@
           <t>9</t>
         </is>
       </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>KIM-0050_izah.png</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -6462,7 +6759,9 @@
           <t>B</t>
         </is>
       </c>
-      <c r="N52" s="2" t="inlineStr"/>
+      <c r="N52" s="2" t="n">
+        <v>3</v>
+      </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
           <t>F, $\mathrm{Cl}$, $\mathrm{Br}$, I istiqamətində halogenlərin nisbi atom kütlələri və atom radiusları artır. Bu səbəbdən $\mathrm{A_{r}(X)&lt;A_{r}(Y)}$ olarsa, $\mathrm{r_{1}&lt;r_{2,}}$ və $\mathrm{A_{r}(X)}$ $\mathrm{&gt;A_{r}(Y)}$ olarsa, $\mathrm{r_{1}&gt;r_{2}}$ şərtləri ödənilir.</t>
@@ -6500,7 +6799,7 @@
       </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>xeyr</t>
+          <t>bəli</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
@@ -6516,6 +6815,11 @@
       <c r="Y52" s="2" t="inlineStr">
         <is>
           <t>9</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>KIM-0051_izah.png</t>
         </is>
       </c>
     </row>
@@ -6639,6 +6943,11 @@
       <c r="Y53" s="2" t="inlineStr">
         <is>
           <t>8</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>KIM-0052_izah.png</t>
         </is>
       </c>
     </row>
@@ -6688,7 +6997,9 @@
           <t>36</t>
         </is>
       </c>
-      <c r="N54" s="2" t="inlineStr"/>
+      <c r="N54" s="2" t="n">
+        <v>3</v>
+      </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
           <t>$\mathrm{N_{2} + 3H_{2} \rightarrow 2NH_{3}}$ Reaksiya tənliyindən göründüyü kimi 1k + 3k = 4k mol qaz qarışığı reaksiyaya girən zaman 2k mol qaz əmələ gəlir. Reaksiyaya daxil olan və alınan qaz qarışığının ümumi mol miqdarının azalması 4k – 2k = 2k mol olur. Qrafikə əsasən isə azalma 120 – 96 = 24 moldur. 2k mol azalma-----------3k mol $\mathrm{H_{2}}$ 24 mol azalma-------- x mol $\mathrm{H_{2}}$ x = 36</t>
@@ -6726,7 +7037,7 @@
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>xeyr</t>
+          <t>bəli</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
@@ -6742,6 +7053,11 @@
       <c r="Y54" s="2" t="inlineStr">
         <is>
           <t>9</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>KIM-0053_izah.png</t>
         </is>
       </c>
     </row>
@@ -6843,6 +7159,11 @@
           <t>11</t>
         </is>
       </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>KIM-0054_izah.png</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -6890,7 +7211,9 @@
           <t>19,6</t>
         </is>
       </c>
-      <c r="N56" s="2" t="inlineStr"/>
+      <c r="N56" s="2" t="n">
+        <v>3</v>
+      </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
           <t>8 q x q $\mathrm{NaOH + H_{3}PO_{4} \rightarrow NaH_{2}PO_{4}+}$ $\mathrm{H_{2}O}$ 40 q 98 q 8 q $\mathrm{NaOH}$ - - - - - - x q $\mathrm{H_{3}PO_{4}}$ 40 q $\mathrm{NaOH}$ - - - - - 98 q $\mathrm{H_{3}PO_{4}}$ x = 19,6 q</t>
@@ -6928,7 +7251,7 @@
       </c>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>xeyr</t>
+          <t>bəli</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
@@ -6944,6 +7267,11 @@
       <c r="Y56" s="2" t="inlineStr">
         <is>
           <t>8</t>
+        </is>
+      </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>KIM-0055_izah.png</t>
         </is>
       </c>
     </row>
@@ -7049,6 +7377,11 @@
           <t>7</t>
         </is>
       </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>KIM-0056_izah.png</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -7146,6 +7479,11 @@
       <c r="Y58" s="2" t="inlineStr">
         <is>
           <t>8</t>
+        </is>
+      </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>KIM-0057_izah.png</t>
         </is>
       </c>
     </row>
@@ -7243,6 +7581,11 @@
           <t>8, 9</t>
         </is>
       </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>KIM-0058_izah.png</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -7338,6 +7681,11 @@
           <t>8, 9</t>
         </is>
       </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>KIM-0059_izah.png</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -7433,6 +7781,11 @@
           <t>8, 9</t>
         </is>
       </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>KIM-0060_izah.png</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
@@ -7546,6 +7899,11 @@
           <t>10</t>
         </is>
       </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>KIM-0061_izah.png</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -7613,7 +7971,9 @@
           <t>A</t>
         </is>
       </c>
-      <c r="N63" s="2" t="inlineStr"/>
+      <c r="N63" s="2" t="n">
+        <v>3</v>
+      </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
           <t>$\mathrm{2CO + O_{2} \rightarrow 2CO_{2}}$ reaksiyası üzrə: Reaksiyaya daxil olan maddələrin həcmi =2+1=3 l Reaksiyadan alınan $\mathrm{CO_{2}}$ həcmi = 2 l Fərq = 3-2 = 1 litr Reaksiya tənliyi üzrə 1 litr fərq------2 litr $\mathrm{CO_{2}}$ 20 litr fərq-------x litr CO2/ alınır x = 40 litr</t>
@@ -7651,7 +8011,7 @@
       </c>
       <c r="V63" s="2" t="inlineStr">
         <is>
-          <t>xeyr</t>
+          <t>bəli</t>
         </is>
       </c>
       <c r="W63" s="2" t="inlineStr">
@@ -7667,6 +8027,11 @@
       <c r="Y63" s="2" t="inlineStr">
         <is>
           <t>7</t>
+        </is>
+      </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>KIM-0062_izah.png</t>
         </is>
       </c>
     </row>
@@ -7736,7 +8101,9 @@
           <t>D</t>
         </is>
       </c>
-      <c r="N64" s="2" t="inlineStr"/>
+      <c r="N64" s="2" t="n">
+        <v>3</v>
+      </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
           <t>Azot atomunun elektron formulu $\mathrm{_{7}N}$ .... $\mathrm{1s^{2}/2s^{2}}$ $\mathrm{2p^{3}.}$ Göründüyü kimi, azot atomunun xarici elektron təbəqəsində 5 elektron var. Onda $\mathrm{X^{3+}}$ ionunda 10 elektron var. Deməli, neytral X atomunda 13 elektron var. X atomunun elektron formulundan $\mathrm{(_{13}X}$ $\mathrm{1s^{2}/2s^{2}}$ $\mathrm{2p^{6}/3s^{2}}$ $\mathrm{3p^{1})}$ aydın olur ki, o dövri sistemdə III dövr, III qrupun əsas yarımqrupunda yerləşir.</t>
@@ -7774,7 +8141,7 @@
       </c>
       <c r="V64" s="2" t="inlineStr">
         <is>
-          <t>xeyr</t>
+          <t>bəli</t>
         </is>
       </c>
       <c r="W64" s="2" t="inlineStr">
@@ -7790,6 +8157,11 @@
       <c r="Y64" s="2" t="inlineStr">
         <is>
           <t>8</t>
+        </is>
+      </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>KIM-0063_izah.png</t>
         </is>
       </c>
     </row>
@@ -7905,6 +8277,11 @@
           <t>10</t>
         </is>
       </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>KIM-0064_izah.png</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -8024,6 +8401,11 @@
           <t>8</t>
         </is>
       </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>KIM-0065_izah.png</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -8141,6 +8523,11 @@
       <c r="Y67" s="2" t="inlineStr">
         <is>
           <t>10</t>
+        </is>
+      </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>KIM-0066_izah.png</t>
         </is>
       </c>
     </row>
@@ -8258,6 +8645,11 @@
         </is>
       </c>
       <c r="Y68" s="2" t="inlineStr"/>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>KIM-0067_izah.png</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
@@ -8371,6 +8763,11 @@
           <t>7</t>
         </is>
       </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>KIM-0068_izah.png</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -8438,7 +8835,9 @@
           <t>B</t>
         </is>
       </c>
-      <c r="N70" s="2" t="inlineStr"/>
+      <c r="N70" s="2" t="n">
+        <v>3</v>
+      </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
           <t>Efirləşmə reaksiyasından alınan mürəkkəb efir molekulunda karbon atomlarının ümumi sayı efiri əmələ gətirən spirt və karbon turşusunun molekulunda karbon atomlarının cəminə bərabərdir. Mürəkkəb efirlərin ümumi formulu $\mathrm{C_{y}H_{2y}O_{2}}$ olduğundan y=n+2n=3n karbon atomu olan mürəkkəb efirin formulunu $\mathrm{C_{3n}H_{6n}O_{2}}$ kimi göstərə bilərik. Mürəkkəb efir molekulunda siqma rabitələrin sayını hesabladıqda σ=3n+6n+2-1= 9n+1 alınır</t>
@@ -8476,7 +8875,7 @@
       </c>
       <c r="V70" s="2" t="inlineStr">
         <is>
-          <t>xeyr</t>
+          <t>bəli</t>
         </is>
       </c>
       <c r="W70" s="2" t="inlineStr">
@@ -8492,6 +8891,11 @@
       <c r="Y70" s="2" t="inlineStr">
         <is>
           <t>11</t>
+        </is>
+      </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>KIM-0069_izah.png</t>
         </is>
       </c>
     </row>
@@ -8561,7 +8965,9 @@
           <t>C</t>
         </is>
       </c>
-      <c r="N71" s="2" t="inlineStr"/>
+      <c r="N71" s="2" t="n">
+        <v>3</v>
+      </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
           <t>Dövri sistemdə halogenlərin qrup daxilində yuxarıdan aşağı getdikcə əmələ gətirdiyi bəsit maddələrin molyar kütləsi artdıqca onların reduksiyaedicilik qabiliyyəti artır. Ümumi şəkildə eyni kütlədə götürülmüş halogenlərin $\mathrm{Na}$ ilə reaksiyasına sərf olunan natriumun kütləsini aşağıdakı sxem üzrə hesablamaq olar: a m $\mathrm{Hlg_{2}}$ +2Na → 2NaHlg 46 = a m M M 46 Hesablamadan göründüyü kimi, molyar kütləsi az olan halogenlə reaksiyaya daha çox natrium sərf olunur.</t>
@@ -8599,7 +9005,7 @@
       </c>
       <c r="V71" s="2" t="inlineStr">
         <is>
-          <t>xeyr</t>
+          <t>bəli</t>
         </is>
       </c>
       <c r="W71" s="2" t="inlineStr">
@@ -8615,6 +9021,11 @@
       <c r="Y71" s="2" t="inlineStr">
         <is>
           <t>9</t>
+        </is>
+      </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>KIM-0070_izah.png</t>
         </is>
       </c>
     </row>
@@ -8684,7 +9095,9 @@
           <t>C</t>
         </is>
       </c>
-      <c r="N72" s="2" t="inlineStr"/>
+      <c r="N72" s="2" t="n">
+        <v>3</v>
+      </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
           <t>Cədvəldəki məlumatlara əsasən, elektrolizin ümumi tənliyini aşağıdakı kimi yazmaq olar: $\mathrm{4MeX_{n} + 2nH_{2}O}$ → 4Me + $\mathrm{nO_{2}}$ +4nHX 11,2 litr $\mathrm{O_{2}---------------a}$ mol HX n⋅22,4 litr $\mathrm{O_{2}---------}$ 4n mol HX a= 2 mol</t>
@@ -8722,7 +9135,7 @@
       </c>
       <c r="V72" s="2" t="inlineStr">
         <is>
-          <t>xeyr</t>
+          <t>bəli</t>
         </is>
       </c>
       <c r="W72" s="2" t="inlineStr">
@@ -8738,6 +9151,11 @@
       <c r="Y72" s="2" t="inlineStr">
         <is>
           <t>8</t>
+        </is>
+      </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>KIM-0071_izah.png</t>
         </is>
       </c>
     </row>
@@ -8807,7 +9225,9 @@
           <t>C</t>
         </is>
       </c>
-      <c r="N73" s="2" t="inlineStr"/>
+      <c r="N73" s="2" t="n">
+        <v>3</v>
+      </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
           <t>$\mathrm{CH_{3}OH + CH_{3}COOH}$ $\mathrm{CH \rightarrow _{3}COOCH_{3}+}$ $\mathrm{H_{2}O}$ $\mathrm{H_{2}SO_{4}(q),}$ t $\mathrm{CH_{3}OH + HCl}$ $\mathrm{CH \rightarrow _{3}Cl + H_{2}O}$ $\mathrm{H_{2}SO_{4}(q),t}$ Reaksiyalara əsasən X - $\mathrm{CH_{3}COOCH_{3,}Y}$ isə $\mathrm{CH_{3}Cl}$ maddəsidir.</t>
@@ -8845,7 +9265,7 @@
       </c>
       <c r="V73" s="2" t="inlineStr">
         <is>
-          <t>xeyr</t>
+          <t>bəli</t>
         </is>
       </c>
       <c r="W73" s="2" t="inlineStr">
@@ -8861,6 +9281,11 @@
       <c r="Y73" s="2" t="inlineStr">
         <is>
           <t>11</t>
+        </is>
+      </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>KIM-0072_izah.png</t>
         </is>
       </c>
     </row>
@@ -8930,7 +9355,9 @@
           <t>B</t>
         </is>
       </c>
-      <c r="N74" s="2" t="inlineStr"/>
+      <c r="N74" s="2" t="n">
+        <v>3</v>
+      </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
           <t>Toluol $\mathrm{(C_{7}H_{8})}$ molekulunda 15 atom var və mayedir. Benzol $\mathrm{(C_{6}H_{6})}$ molekulunda 12 atom var və mayedir, $\mathrm{HNO_{3}}$ ilə reaksiyanın tipi- əvəzetmə Fenol $\mathrm{(C_{6}H_{5}OH)}$ molekulunda 13 atom var və bərkdir. Anilin $\mathrm{(C_{6}H_{5}NH_{2})}$ molekulunda 14 atom var və mayedir. Propen $\mathrm{(C_{3}H_{6})}$ molekulunda 9 atom var və qazdır.</t>
@@ -8968,7 +9395,7 @@
       </c>
       <c r="V74" s="2" t="inlineStr">
         <is>
-          <t>xeyr</t>
+          <t>bəli</t>
         </is>
       </c>
       <c r="W74" s="2" t="inlineStr">
@@ -8984,6 +9411,11 @@
       <c r="Y74" s="2" t="inlineStr">
         <is>
           <t>10</t>
+        </is>
+      </c>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>KIM-0073_izah.png</t>
         </is>
       </c>
     </row>
@@ -9053,7 +9485,9 @@
           <t>E</t>
         </is>
       </c>
-      <c r="N75" s="2" t="inlineStr"/>
+      <c r="N75" s="2" t="n">
+        <v>3</v>
+      </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
           <t>Le-Şatelye prinsipinə görə tarazlıqda olan sistemə xaricdən təsir edildikdə kimyəvi tarazlıq sistemdə həmin təsirin azaldığı tərəfə yönəlir. Verilmiş dönən reaksiyada sola gedən reaksiya endotermikdir və sistemdə təzyiqin artması ilə baş verir. Bunlara əsasən , $\mathrm{N_{2}+}$ $\mathrm{3H_{2} \Leftrightarrow 2NH_{3}+}$ Q reaksiyasında tarazlığı ilkin maddələrin alınması istiqamətinə yönəltmək üçün temperaturu artırmaq, təzyiqi azaltmaq lazımdır.</t>
@@ -9091,7 +9525,7 @@
       </c>
       <c r="V75" s="2" t="inlineStr">
         <is>
-          <t>xeyr</t>
+          <t>bəli</t>
         </is>
       </c>
       <c r="W75" s="2" t="inlineStr">
@@ -9107,6 +9541,11 @@
       <c r="Y75" s="2" t="inlineStr">
         <is>
           <t>8</t>
+        </is>
+      </c>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t>KIM-0074_izah.png</t>
         </is>
       </c>
     </row>
@@ -9232,6 +9671,11 @@
           <t>9</t>
         </is>
       </c>
+      <c r="Z76" t="inlineStr">
+        <is>
+          <t>KIM-0075_izah.png</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -9351,6 +9795,11 @@
           <t>11</t>
         </is>
       </c>
+      <c r="Z77" t="inlineStr">
+        <is>
+          <t>KIM-0076_izah.png</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -9472,6 +9921,11 @@
       <c r="Y78" s="2" t="inlineStr">
         <is>
           <t>9</t>
+        </is>
+      </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>KIM-0077_izah.png</t>
         </is>
       </c>
     </row>
@@ -9593,6 +10047,11 @@
           <t>9</t>
         </is>
       </c>
+      <c r="Z79" t="inlineStr">
+        <is>
+          <t>KIM-0078_izah.png</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -9660,7 +10119,9 @@
           <t>E</t>
         </is>
       </c>
-      <c r="N80" s="2" t="inlineStr"/>
+      <c r="N80" s="2" t="n">
+        <v>3</v>
+      </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
           <t>Qeyd edilən maddə α-alaninin dipeptididir. Dipeptid molekulunda 1 peptid rabitəsi olur, bir molunun hidrolizi zamanı 1 mol su sərf olunur və 2 mol aminturşu əmələ gəlir.</t>
@@ -9698,7 +10159,7 @@
       </c>
       <c r="V80" s="2" t="inlineStr">
         <is>
-          <t>xeyr</t>
+          <t>bəli</t>
         </is>
       </c>
       <c r="W80" s="2" t="inlineStr">
@@ -9714,6 +10175,11 @@
       <c r="Y80" s="2" t="inlineStr">
         <is>
           <t>11</t>
+        </is>
+      </c>
+      <c r="Z80" t="inlineStr">
+        <is>
+          <t>KIM-0079_izah.png</t>
         </is>
       </c>
     </row>
@@ -9829,6 +10295,11 @@
           <t>9</t>
         </is>
       </c>
+      <c r="Z81" t="inlineStr">
+        <is>
+          <t>KIM-0080_izah.png</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="3" t="inlineStr">
@@ -9942,6 +10413,11 @@
           <t>11</t>
         </is>
       </c>
+      <c r="Z82" t="inlineStr">
+        <is>
+          <t>KIM-0081_izah.png</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -10009,7 +10485,9 @@
           <t>B</t>
         </is>
       </c>
-      <c r="N83" s="2" t="inlineStr"/>
+      <c r="N83" s="2" t="n">
+        <v>3</v>
+      </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
           <t>Sxemdən göründüyü kimi, X - $\mathrm{NaOH}$, Y - $\mathrm{Na_{2}SiO_{3}-}$ dür. $\mathrm{Na_{2}SiO_{3} + 2HCl \rightarrow 2NaCl + H_{2}SiO_{3}(Z)}$</t>
@@ -10043,7 +10521,7 @@
       </c>
       <c r="V83" s="2" t="inlineStr">
         <is>
-          <t>xeyr</t>
+          <t>bəli</t>
         </is>
       </c>
       <c r="W83" s="2" t="inlineStr">
@@ -10059,6 +10537,11 @@
       <c r="Y83" s="2" t="inlineStr">
         <is>
           <t>9</t>
+        </is>
+      </c>
+      <c r="Z83" t="inlineStr">
+        <is>
+          <t>KIM-0082_izah.png</t>
         </is>
       </c>
     </row>
@@ -10154,6 +10637,11 @@
           <t>9</t>
         </is>
       </c>
+      <c r="Z84" t="inlineStr">
+        <is>
+          <t>KIM-0083_izah.png</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="3" t="inlineStr">
@@ -10247,6 +10735,11 @@
           <t>11</t>
         </is>
       </c>
+      <c r="Z85" t="inlineStr">
+        <is>
+          <t>KIM-0084_izah.png</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -10294,7 +10787,9 @@
           <t>2,4</t>
         </is>
       </c>
-      <c r="N86" s="2" t="inlineStr"/>
+      <c r="N86" s="2" t="n">
+        <v>3</v>
+      </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
           <t>$\mathrm{1.X_{1} \rightarrow X_{2}}$ keçidi zamanı məhlulun qatılığı və kütləsi artmışdır. Deməli, məhlula duz əlavə olunub 2. $\mathrm{X_{1} \rightarrow X_{3}}$ keçidi zamanı məhlulun qatılığı azalır, kütləsi artır. Deməli, məhlula su əlavə olunub və ya həmin duzun fərqli qatılıqda məhlulu əlavə olunub. $\mathrm{3.X_{3} \rightarrow X_{1}}$ keçidi zamanı məhlulun qatılığı artır, kütləsi azalır. Deməli məhluldan su buxarlanır $\mathrm{4.X_{2} \rightarrow X_{1}}$ keçidi zamanı məhlula su əlavə olunsa idi , məhlulun kütləsi artacaqdır</t>
@@ -10332,7 +10827,7 @@
       </c>
       <c r="V86" s="2" t="inlineStr">
         <is>
-          <t>xeyr</t>
+          <t>bəli</t>
         </is>
       </c>
       <c r="W86" s="2" t="inlineStr">
@@ -10348,6 +10843,11 @@
       <c r="Y86" s="2" t="inlineStr">
         <is>
           <t>7</t>
+        </is>
+      </c>
+      <c r="Z86" t="inlineStr">
+        <is>
+          <t>KIM-0085_izah.png</t>
         </is>
       </c>
     </row>
@@ -10443,6 +10943,11 @@
           <t>9</t>
         </is>
       </c>
+      <c r="Z87" t="inlineStr">
+        <is>
+          <t>KIM-0086_izah.png</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
@@ -10544,6 +11049,11 @@
       <c r="Y88" s="2" t="inlineStr">
         <is>
           <t>9</t>
+        </is>
+      </c>
+      <c r="Z88" t="inlineStr">
+        <is>
+          <t>KIM-0087_izah.png</t>
         </is>
       </c>
     </row>
@@ -10629,6 +11139,11 @@
         </is>
       </c>
       <c r="Y89" s="2" t="inlineStr"/>
+      <c r="Z89" t="inlineStr">
+        <is>
+          <t>KIM-0088_izah.png</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
@@ -10712,6 +11227,11 @@
         </is>
       </c>
       <c r="Y90" s="2" t="inlineStr"/>
+      <c r="Z90" t="inlineStr">
+        <is>
+          <t>KIM-0089_izah.png</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
@@ -10795,6 +11315,11 @@
         </is>
       </c>
       <c r="Y91" s="2" t="inlineStr"/>
+      <c r="Z91" t="inlineStr">
+        <is>
+          <t>KIM-0090_izah.png</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
@@ -10862,7 +11387,9 @@
           <t>D</t>
         </is>
       </c>
-      <c r="N92" s="2" t="inlineStr"/>
+      <c r="N92" s="2" t="n">
+        <v>3</v>
+      </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
           <t>Etanol suda həll olan mayedir və su ilə eynicinsli qarışıq əmələ gətirir. Məlumdur ki, bir birində həll olan maye maddələri bir-birindən ayırmaq üçün distillə üsulundan istifadə olunur.</t>
@@ -10900,7 +11427,7 @@
       </c>
       <c r="V92" s="2" t="inlineStr">
         <is>
-          <t>xeyr</t>
+          <t>bəli</t>
         </is>
       </c>
       <c r="W92" s="2" t="inlineStr">
@@ -10916,6 +11443,11 @@
       <c r="Y92" s="2" t="inlineStr">
         <is>
           <t>7</t>
+        </is>
+      </c>
+      <c r="Z92" t="inlineStr">
+        <is>
+          <t>KIM-0091_izah.png</t>
         </is>
       </c>
     </row>
@@ -11031,6 +11563,11 @@
           <t>8</t>
         </is>
       </c>
+      <c r="Z93" t="inlineStr">
+        <is>
+          <t>KIM-0092_izah.png</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
@@ -11098,7 +11635,9 @@
           <t>E</t>
         </is>
       </c>
-      <c r="N94" s="2" t="inlineStr"/>
+      <c r="N94" s="2" t="n">
+        <v>3</v>
+      </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
           <t>A) $\mathrm{FeS_{2} + O_{2}}$ t → $\mathrm{Fe_{2}O_{3}+SO_{2}}$ B) $\mathrm{CaCO_{3}}$ t → $\mathrm{CaO}$ $\mathrm{+CO_{2}}$ C) $\mathrm{NH_{3} + O_{2}}$ t → $\mathrm{N_{2}}$ $\mathrm{+H_{2}O}$ D) $\mathrm{H_{2}S + O_{2}}$ t → $\mathrm{SO_{2}}$ $\mathrm{+H_{2}O}$ E) $\mathrm{Mg(OH)_{2}}$ t → $\mathrm{MgO}$ $\mathrm{+H_{2}O}$ Verilən reaksiya sxemlərində göründüyü kimi $\mathrm{FeS_{2} + O_{2}}$ t → $\mathrm{Fe_{2}O_{3}+SO_{2}}$ reaksiyasından alınan $\mathrm{Fe_{2}O_{3}}$ amfoter , $\mathrm{SO_{2}}$ isə turşu oksididir. Bu maddələrin ikisi $\mathrm{NaOH}$ məhlulu ilə reaksiyaya daxil olur.</t>
@@ -11132,7 +11671,7 @@
       </c>
       <c r="V94" s="2" t="inlineStr">
         <is>
-          <t>xeyr</t>
+          <t>bəli</t>
         </is>
       </c>
       <c r="W94" s="2" t="inlineStr">
@@ -11148,6 +11687,11 @@
       <c r="Y94" s="2" t="inlineStr">
         <is>
           <t>8</t>
+        </is>
+      </c>
+      <c r="Z94" t="inlineStr">
+        <is>
+          <t>KIM-0093_izah.png</t>
         </is>
       </c>
     </row>
@@ -11217,7 +11761,9 @@
           <t>C</t>
         </is>
       </c>
-      <c r="N95" s="2" t="inlineStr"/>
+      <c r="N95" s="2" t="n">
+        <v>3</v>
+      </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
           <t>Şərtə əsasən yalnız $\mathrm{K_{2}CO_{3}+2HCl \rightarrow KCl}$ $\mathrm{+CO_{2}}$ $\mathrm{+H_{2}O}$ reaksiyasında $\mathrm{CO_{2}}$ alınır.</t>
@@ -11255,7 +11801,7 @@
       </c>
       <c r="V95" s="2" t="inlineStr">
         <is>
-          <t>xeyr</t>
+          <t>bəli</t>
         </is>
       </c>
       <c r="W95" s="2" t="inlineStr">
@@ -11271,6 +11817,11 @@
       <c r="Y95" s="2" t="inlineStr">
         <is>
           <t>9</t>
+        </is>
+      </c>
+      <c r="Z95" t="inlineStr">
+        <is>
+          <t>KIM-0094_izah.png</t>
         </is>
       </c>
     </row>
@@ -11340,7 +11891,9 @@
           <t>E</t>
         </is>
       </c>
-      <c r="N96" s="2" t="inlineStr"/>
+      <c r="N96" s="2" t="n">
+        <v>3</v>
+      </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
           <t>Qələvi metalların xlorid turşusu ilə reaksiyasını ümumi şəkildə 2Me+2HCl → 2MeCl + $\mathrm{H_{2}}$ tənliyi ilə ifadə edə bilərik. Tənliyə əsasən hesablama aparsaq $\mathrm{2A_{r}(Me)------------1}$ mol $\mathrm{H_{2}}$ 9,8 q Me-------0,7 mol $\mathrm{H_{2}}$ $\mathrm{A_{r}(Me)}$ =7. Metalın nisbi atom kütləsi 7-dir.</t>
@@ -11378,7 +11931,7 @@
       </c>
       <c r="V96" s="2" t="inlineStr">
         <is>
-          <t>xeyr</t>
+          <t>bəli</t>
         </is>
       </c>
       <c r="W96" s="2" t="inlineStr">
@@ -11394,6 +11947,11 @@
       <c r="Y96" s="2" t="inlineStr">
         <is>
           <t>9</t>
+        </is>
+      </c>
+      <c r="Z96" t="inlineStr">
+        <is>
+          <t>KIM-0095_izah.png</t>
         </is>
       </c>
     </row>
@@ -11503,6 +12061,11 @@
           <t>10</t>
         </is>
       </c>
+      <c r="Z97" t="inlineStr">
+        <is>
+          <t>KIM-0096_izah.png</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
@@ -11570,7 +12133,9 @@
           <t>A</t>
         </is>
       </c>
-      <c r="N98" s="2" t="inlineStr"/>
+      <c r="N98" s="2" t="n">
+        <v>3</v>
+      </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
           <t>$\mathrm{OH}$ + nH C H → O n t, $\mathrm{H^{+}}$ reaksiyası üzrə fenol və formaldehid birlikdə polikondensləşərək polimerlərə aid olan fenolformaldehid qatranı və su əmələ gətirir.</t>
@@ -11608,7 +12173,7 @@
       </c>
       <c r="V98" s="2" t="inlineStr">
         <is>
-          <t>xeyr</t>
+          <t>bəli</t>
         </is>
       </c>
       <c r="W98" s="2" t="inlineStr">
@@ -11624,6 +12189,11 @@
       <c r="Y98" s="2" t="inlineStr">
         <is>
           <t>11</t>
+        </is>
+      </c>
+      <c r="Z98" t="inlineStr">
+        <is>
+          <t>KIM-0097_izah.png</t>
         </is>
       </c>
     </row>
@@ -11739,6 +12309,11 @@
           <t>8</t>
         </is>
       </c>
+      <c r="Z99" t="inlineStr">
+        <is>
+          <t>KIM-0098_izah.png</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="3" t="inlineStr">
@@ -11852,6 +12427,11 @@
           <t>7</t>
         </is>
       </c>
+      <c r="Z100" t="inlineStr">
+        <is>
+          <t>KIM-0099_izah.png</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="3" t="inlineStr">
@@ -11965,6 +12545,11 @@
           <t>9</t>
         </is>
       </c>
+      <c r="Z101" t="inlineStr">
+        <is>
+          <t>KIM-0100_izah.png</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
@@ -12032,7 +12617,9 @@
           <t>A</t>
         </is>
       </c>
-      <c r="N102" s="2" t="inlineStr"/>
+      <c r="N102" s="2" t="n">
+        <v>3</v>
+      </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
           <t>$\mathrm{Fe + 2HCl \rightarrow FeCl_{2}+}$ $\mathrm{H_{2}}$ $\mathrm{(X_{2})}$ 2 $\mathrm{KMnO_{4}t \rightarrow K_{2}MnO_{4} + MnO_{2}+}$ $\mathrm{O_{2}(Y_{2})}$ 6 3 $\mathrm{2H_{2} + O_{2} \rightarrow 2H_{2}O}$ 2 1 Tənliyə əsasən 7 mol $\mathrm{H_{2}}$ və 3 mol $\mathrm{O_{2}}$ tam reaksiyaya daxil olduqda, oksigenin hamısı sərf olunur və 1 mol $\mathrm{H_{2}(7-6=1)}$ artıq qalır</t>
@@ -12070,7 +12657,7 @@
       </c>
       <c r="V102" s="2" t="inlineStr">
         <is>
-          <t>xeyr</t>
+          <t>bəli</t>
         </is>
       </c>
       <c r="W102" s="2" t="inlineStr">
@@ -12086,6 +12673,11 @@
       <c r="Y102" s="2" t="inlineStr">
         <is>
           <t>7</t>
+        </is>
+      </c>
+      <c r="Z102" t="inlineStr">
+        <is>
+          <t>KIM-0101_izah.png</t>
         </is>
       </c>
     </row>
@@ -12155,7 +12747,9 @@
           <t>A</t>
         </is>
       </c>
-      <c r="N103" s="2" t="inlineStr"/>
+      <c r="N103" s="2" t="n">
+        <v>3</v>
+      </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
           <t>Aldehidlərin hidrogenlə reaksiyasından molekulunda eyni sayda karbon atomu olan birli spirtlər alınır. t, kat → $\mathrm{CH_{3}}$ C O H $\mathrm{+H_{2}}$ reaksiyasından etil spirtinin $\mathrm{(C_{2}H_{5}OH)}$ alındığı məlum olur. $\mathrm{X=C_{2}H_{5}OH,}$ etil spirti.</t>
@@ -12193,7 +12787,7 @@
       </c>
       <c r="V103" s="2" t="inlineStr">
         <is>
-          <t>xeyr</t>
+          <t>bəli</t>
         </is>
       </c>
       <c r="W103" s="2" t="inlineStr">
@@ -12209,6 +12803,11 @@
       <c r="Y103" s="2" t="inlineStr">
         <is>
           <t>11</t>
+        </is>
+      </c>
+      <c r="Z103" t="inlineStr">
+        <is>
+          <t>KIM-0102_izah.png</t>
         </is>
       </c>
     </row>
@@ -12278,7 +12877,9 @@
           <t>B</t>
         </is>
       </c>
-      <c r="N104" s="2" t="inlineStr"/>
+      <c r="N104" s="2" t="n">
+        <v>3</v>
+      </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
           <t>Ketonlar $\mathrm{C_{n}H_{2n}O}$ ümumi formuluna malikdir. Doymuş alifatik ketonların homoloji sırasının birinci nümayəndəsinin molekulunda 3 karbon atomu var. Deməli, homoloji sıranın üçüncü nümayəndəsinin molekulunda 5 karbon atomu olacaq.</t>
@@ -12316,7 +12917,7 @@
       </c>
       <c r="V104" s="2" t="inlineStr">
         <is>
-          <t>xeyr</t>
+          <t>bəli</t>
         </is>
       </c>
       <c r="W104" s="2" t="inlineStr">
@@ -12332,6 +12933,11 @@
       <c r="Y104" s="2" t="inlineStr">
         <is>
           <t>11</t>
+        </is>
+      </c>
+      <c r="Z104" t="inlineStr">
+        <is>
+          <t>KIM-0103_izah.png</t>
         </is>
       </c>
     </row>
@@ -12457,6 +13063,11 @@
           <t>10</t>
         </is>
       </c>
+      <c r="Z105" t="inlineStr">
+        <is>
+          <t>KIM-0104_izah.png</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
@@ -12574,6 +13185,11 @@
       <c r="Y106" s="2" t="inlineStr">
         <is>
           <t>9</t>
+        </is>
+      </c>
+      <c r="Z106" t="inlineStr">
+        <is>
+          <t>KIM-0105_izah.png</t>
         </is>
       </c>
     </row>
@@ -12689,6 +13305,11 @@
           <t>7</t>
         </is>
       </c>
+      <c r="Z107" t="inlineStr">
+        <is>
+          <t>KIM-0106_izah.png</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
@@ -12812,6 +13433,11 @@
           <t>9</t>
         </is>
       </c>
+      <c r="Z108" t="inlineStr">
+        <is>
+          <t>KIM-0107_izah.png</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
@@ -12879,7 +13505,9 @@
           <t>C</t>
         </is>
       </c>
-      <c r="N109" s="2" t="inlineStr"/>
+      <c r="N109" s="2" t="n">
+        <v>3</v>
+      </c>
       <c r="O109" s="2" t="inlineStr">
         <is>
           <t>44,8 litr 22,4 litr 60 2 $\mathrm{NH_{3} + CO_{2} \rightarrow CO(NH_{2})_{2}}$ $\mathrm{+H_{2}O}$ x litr 22,4 litr 15 verilən $\mathrm{CO_{2}}$ qaz artıq miqdarda götürülüb. Göründüyü kimi, 22,4 litr $\mathrm{CO_{2}}$-dən reaksiyaya 4 dəfə az, yəni 5,6 litr qaz daxil olur. 44,8 litr ------ 60 q CO(N $\mathrm{H_{2})_{2}}$ x litr -------- 15 q CO(N $\mathrm{H_{2})_{2}}$ / x=11,2 litr (n.ş) $\mathrm{NH_{3}}$ tam reaksiyaya daxil olur</t>
@@ -12917,7 +13545,7 @@
       </c>
       <c r="V109" s="2" t="inlineStr">
         <is>
-          <t>xeyr</t>
+          <t>bəli</t>
         </is>
       </c>
       <c r="W109" s="2" t="inlineStr">
@@ -12933,6 +13561,11 @@
       <c r="Y109" s="2" t="inlineStr">
         <is>
           <t>9</t>
+        </is>
+      </c>
+      <c r="Z109" t="inlineStr">
+        <is>
+          <t>KIM-0108_izah.png</t>
         </is>
       </c>
     </row>
@@ -13052,6 +13685,11 @@
       <c r="Y110" s="2" t="inlineStr">
         <is>
           <t>9</t>
+        </is>
+      </c>
+      <c r="Z110" t="inlineStr">
+        <is>
+          <t>KIM-0109_izah.png</t>
         </is>
       </c>
     </row>
@@ -13167,6 +13805,11 @@
           <t>11</t>
         </is>
       </c>
+      <c r="Z111" t="inlineStr">
+        <is>
+          <t>KIM-0110_izah.png</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="3" t="inlineStr">
@@ -13280,6 +13923,11 @@
           <t>10</t>
         </is>
       </c>
+      <c r="Z112" t="inlineStr">
+        <is>
+          <t>KIM-0111_izah.png</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="3" t="inlineStr">
@@ -13391,6 +14039,11 @@
       <c r="Y113" s="3" t="inlineStr">
         <is>
           <t>8</t>
+        </is>
+      </c>
+      <c r="Z113" t="inlineStr">
+        <is>
+          <t>KIM-0112_izah.png</t>
         </is>
       </c>
     </row>
@@ -13486,6 +14139,11 @@
           <t>10</t>
         </is>
       </c>
+      <c r="Z114" t="inlineStr">
+        <is>
+          <t>KIM-0113_izah.png</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
@@ -13533,7 +14191,9 @@
           <t>1,3</t>
         </is>
       </c>
-      <c r="N115" s="2" t="inlineStr"/>
+      <c r="N115" s="2" t="n">
+        <v>3</v>
+      </c>
       <c r="O115" s="2" t="inlineStr">
         <is>
           <t>Məlumdur ki, ikili spirtlərin $\mathrm{CuO}$ ilə reaksiyasından ketonlar alınır. Verilmiş reaksiyalardan yalnız birinci və üçüncü reaksiyalarda götürülən spirtlər ikilidir. Deməli, birinci və üçüncü reaksiyalardan keton alınacaq.</t>
@@ -13571,7 +14231,7 @@
       </c>
       <c r="V115" s="2" t="inlineStr">
         <is>
-          <t>xeyr</t>
+          <t>bəli</t>
         </is>
       </c>
       <c r="W115" s="2" t="inlineStr">
@@ -13587,6 +14247,11 @@
       <c r="Y115" s="2" t="inlineStr">
         <is>
           <t>11</t>
+        </is>
+      </c>
+      <c r="Z115" t="inlineStr">
+        <is>
+          <t>KIM-0114_izah.png</t>
         </is>
       </c>
     </row>
@@ -13682,6 +14347,11 @@
           <t>7</t>
         </is>
       </c>
+      <c r="Z116" t="inlineStr">
+        <is>
+          <t>KIM-0115_izah.png</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
@@ -13729,7 +14399,9 @@
           <t>420</t>
         </is>
       </c>
-      <c r="N117" s="2" t="inlineStr"/>
+      <c r="N117" s="2" t="n">
+        <v>3</v>
+      </c>
       <c r="O117" s="2" t="inlineStr">
         <is>
           <t>Azotdan nitrat turşusunun alınması sadə sxemlə ifadə etsək $\mathrm{N_{2} \rightarrow 2HNO_{3}}$ 22,4 litr (n.ş) $\mathrm{N_{2}---------126}$ q $\mathrm{HNO_{3}}$ alınır 44,8 litr (n.ş) $\mathrm{N_{2}}$ -----------x q $\mathrm{HNO_{3}}$ x= 252 q 252-------------60% y ---------------100% y=420 q</t>
@@ -13763,7 +14435,7 @@
       </c>
       <c r="V117" s="2" t="inlineStr">
         <is>
-          <t>xeyr</t>
+          <t>bəli</t>
         </is>
       </c>
       <c r="W117" s="2" t="inlineStr">
@@ -13779,6 +14451,11 @@
       <c r="Y117" s="2" t="inlineStr">
         <is>
           <t>9</t>
+        </is>
+      </c>
+      <c r="Z117" t="inlineStr">
+        <is>
+          <t>KIM-0116_izah.png</t>
         </is>
       </c>
     </row>
@@ -13884,6 +14561,11 @@
           <t>8</t>
         </is>
       </c>
+      <c r="Z118" t="inlineStr">
+        <is>
+          <t>KIM-0117_izah.png</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
@@ -13987,6 +14669,11 @@
           <t>7</t>
         </is>
       </c>
+      <c r="Z119" t="inlineStr">
+        <is>
+          <t>KIM-0118_izah.png</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
@@ -14090,6 +14777,11 @@
           <t>9</t>
         </is>
       </c>
+      <c r="Z120" t="inlineStr">
+        <is>
+          <t>KIM-0119_izah.png</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
@@ -14191,6 +14883,11 @@
       <c r="Y121" s="2" t="inlineStr">
         <is>
           <t>10</t>
+        </is>
+      </c>
+      <c r="Z121" t="inlineStr">
+        <is>
+          <t>KIM-0120_izah.png</t>
         </is>
       </c>
     </row>
